--- a/Plotting/Results_excels/production_shares_ammonia_Scope1-3_FPO.xlsx
+++ b/Plotting/Results_excels/production_shares_ammonia_Scope1-3_FPO.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,27 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Iteration_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -535,11 +556,56 @@
           <t>2050</t>
         </is>
       </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -552,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1184000.000000336</v>
+        <v>1184000.000000149</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -561,19 +627,46 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1183999.999999999</v>
+        <v>1183999.999999925</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1184000.000000159</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1183999.999999937</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1184000.00000002</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -601,6 +694,33 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -620,22 +740,49 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.770566735500337e-08</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1179579.064985031</v>
+        <v>1179567.528858795</v>
       </c>
       <c r="G6" t="n">
-        <v>1179252.032747442</v>
+        <v>1179237.727300087</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1179595.24366186</v>
+        <v>1178788.6409718</v>
       </c>
       <c r="J6" t="n">
-        <v>1179261.623616016</v>
+        <v>1180009.229801814</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1178788.810753546</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1180009.225566907</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.526539279723923e-07</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1179671.733515162</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1180009.559251296</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1178784.011661825</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1180009.34527204</v>
       </c>
     </row>
     <row r="7">
@@ -671,6 +818,33 @@
       <c r="J7" t="n">
         <v>0</v>
       </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.866940174742638e-09</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.869079863506741e-09</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -705,6 +879,33 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -739,6 +940,33 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -773,6 +1001,33 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -807,6 +1062,33 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -841,6 +1123,33 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -875,6 +1184,33 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -909,6 +1245,33 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -943,12 +1306,42 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="E1:G1"/>
+    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
